--- a/docs/decisions/business-rules-ledger.xlsx
+++ b/docs/decisions/business-rules-ledger.xlsx
@@ -295,7 +295,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ClosureAuditDecisionsTable" displayName="ClosureAuditDecisionsTable" ref="A1:E7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ClosureAuditDecisionsTable" displayName="ClosureAuditDecisionsTable" ref="A1:E17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="5">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Decision"/>
@@ -7392,7 +7392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="26" min="1" max="1"/>
@@ -7780,6 +7780,87 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>R20</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Business Timezone</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>The business timezone is Africa/Cairo, including daylight saving time when Egypt applies it. Timestamps are stored in UTC. Calendar-day concepts (analytics Today/Yesterday/ranges, the return window) use Africa/Cairo.</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Owner decision (TASK-005). Clarifies DB Design §1 principle 10, Q17 and Q149. Business Spec R20.</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>R21</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Day Counting</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Return window: a return may be requested until the end of the 14th calendar day after the delivery date in Africa/Cairo (delivery day is day 0). COD confirmation maximum: an exact elapsed duration of at most 72 hours from order creation; the configurable timeout can never exceed 72 hours.</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Owner decision (TASK-005). Clarifies Q17 and Q25. Business Spec R21.</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>R22</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>HALF-UP on Negative Amounts</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>HALF-UP rounding ties round away from zero for negative amounts too (2.5 → 3, -2.5 → -3).</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Owner decision (TASK-005). Clarifies R9. Business Spec R22.</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/docs/decisions/business-rules-ledger.xlsx
+++ b/docs/decisions/business-rules-ledger.xlsx
@@ -295,7 +295,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ClosureAuditDecisionsTable" displayName="ClosureAuditDecisionsTable" ref="A1:E17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ClosureAuditDecisionsTable" displayName="ClosureAuditDecisionsTable" ref="A1:E22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="5">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Decision"/>
@@ -7392,7 +7392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="26" min="1" max="1"/>
@@ -7861,6 +7861,141 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>R23</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Sessions After Password Reset / Change</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>A password reset revokes all of the customer's sessions. A password change while logged in keeps the current session and revokes all others. A customer session lasts 30 days from login; the lifetime is absolute (refreshing does not extend it).</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Owner decision (TASK-007 + plan review). Completes User Flows §3.2; clarifies Q162, Q164. Resolves TASK-002A open decision 2 for customers. Business Spec R23.</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>R24</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Login Throttling</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>5 consecutive failed password attempts on an account block that account's login for 15 minutes; the correct password is also refused during the block; the count resets on a successful login and after the block; wrong current passwords during a password change count. Per IP: 30 failed logins within 15 minutes block logins from that IP for 15 minutes. CAPTCHA is added later (TASK-061).</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Owner decision (TASK-007 + plan review); per-IP threshold proposed in TASK-007 (ADR-0013) and approved. Implements Q157. Business Spec R24.</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>R25</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Phone Verification &amp; Account Activation</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>At registration the phone is verified by a WhatsApp OTP and the email by an email OTP; the account becomes ACTIVE only after both. Registration requires email, phone, password and full name. WhatsApp is also the OTP channel for phone change and guest-order claim. Pending registrations do not reserve identifiers: email/phone uniqueness applies only to verified identities (Q151 applies to a verified email). A PENDING_VERIFICATION account expires 24 hours after registration. A new registration replaces a pending account whose email and phone are both unverified, or any expired pending account; a pending account with a verified email keeps it, and whichever account verifies a shared unverified phone first keeps it.</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Owner decision (TASK-007 + plan review). Extends Q41, Q42, Q44, Q151, Q153. Resolves TASK-002A open decision 3. Business Spec R25.</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>R26</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Unverified Email Cannot Log In</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>A customer whose email is not verified cannot log in. A customer whose email is verified but whose phone is not yet verified (pending, within 24 hours) can log in with access limited to session actions and verification steps; everything else requires an ACTIVE account.</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Owner decision (TASK-007 + plan review). Business Spec R26.</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>R27</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Customer Phone Format</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Customer phone numbers are Egyptian mobile numbers only (010, 011, 012 or 015 followed by 8 digits), stored normalized in E.164 (+20…). Accepted input forms: 01xxxxxxxxx, +201xxxxxxxxx, 00201xxxxxxxxx.</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Owner decision (TASK-007 plan review). Clarifies Q41, R13. Business Spec R27.</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/docs/decisions/business-rules-ledger.xlsx
+++ b/docs/decisions/business-rules-ledger.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BeautyFits Q1-Q185" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closure C1-C6" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Corrections" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closure &amp; Audit Decisions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="BeautyFits Q1-Q185" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Closure C1-C6" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Audit Corrections" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Closure &amp; Audit Decisions" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -7392,7 +7392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="26" min="1" max="1"/>
@@ -7996,6 +7996,114 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>R28</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Employee Second Factor</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Every employee, Owner/Admin included, logs in with email + password + email OTP. A successful OTP trusts that device for 30 days; after 30 days or on a new device the OTP is required again. No separate MFA factor in v1.</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Owner decision (2026-10-01, project thread). Amends Q165. Business Spec R28.</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>R29</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Staff Sessions</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Default staff session: 12 hours maximum, ended after 60 minutes without activity; both configurable by the Owner/Admin. A staff password reset revokes all of the employee's sessions (as R23 for customers).</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Owner decision (2026-10-01, project thread). Clarifies Q163. Business Spec R29.</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Email as the Only OTP Channel</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Email is the only OTP channel in v1 for customers and employees (SMS/WhatsApp OTP cost more). Phone change: re-authenticate, OTP to the verified account email, change phone, notify the verified email. Email change unchanged (Q152). Registration phone verification: BUSINESS DECISION REQUIRED.</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Owner decision (2026-10-01, project thread). Amends Q153 and the WhatsApp channel of R25. Business Spec R30.</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>R31</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Guest Order Claim OTP</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>The claim OTP is emailed to the guest_email stored on the guest order(s). Only guest orders whose phone and email both match the account are linked; others are linked through support. Phone match alone is never sufficient.</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>Owner decision (2026-10-01, project thread). Clarifies Q43/Q44 and User Flows §3.5; replaces the WhatsApp channel of R25. Business Spec R31.</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/docs/decisions/business-rules-ledger.xlsx
+++ b/docs/decisions/business-rules-ledger.xlsx
@@ -8063,12 +8063,12 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Email is the only OTP channel in v1 for customers and employees (SMS/WhatsApp OTP cost more). Phone change: re-authenticate, OTP to the verified account email, change phone, notify the verified email. Email change unchanged (Q152). Registration phone verification: BUSINESS DECISION REQUIRED.</t>
+          <t>Email is the only OTP channel in v1 for customers and employees (SMS/WhatsApp OTP cost more). Phone change: re-authenticate, OTP to the verified account email, change phone, notify the verified email. Email change unchanged (Q152). Registration: no phone OTP; the account is ACTIVE once the email is verified; the phone stays required, Egyptian and unique among active accounts.</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Owner decision (2026-10-01, project thread). Amends Q153 and the WhatsApp channel of R25. Business Spec R30.</t>
+          <t>Owner decision (2026-10-01, project thread). Amends Q153, R25 (WhatsApp phone OTP and activation) and R26. Business Spec R30.</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">

--- a/docs/decisions/business-rules-ledger.xlsx
+++ b/docs/decisions/business-rules-ledger.xlsx
@@ -295,7 +295,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ClosureAuditDecisionsTable" displayName="ClosureAuditDecisionsTable" ref="A1:E22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ClosureAuditDecisionsTable" displayName="ClosureAuditDecisionsTable" ref="A1:E30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="5">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Decision"/>
@@ -7392,7 +7392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="26" min="1" max="1"/>
@@ -8104,6 +8104,114 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>R32</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Governorates and Areas as a Managed List</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Governorates and their areas form one managed location list shared by customer addresses and shipping rules (Q122); no free text. The 27 Egyptian governorates are preloaded; the Owner/Admin (SHIPPING_MANAGE) adds, renames and deactivates areas. An address names one governorate and one of its areas; deactivated governorates/areas can no longer be chosen, existing addresses keep them.</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Owner decision (2026-10-04, TASK-009). Answers TASK-002A open decision 7. Business Spec R32.</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>R33</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Cart Merge After Login</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>When a guest cart is merged into the customer cart, an item present in both gets the sum of the two quantities, capped at the quantity available for that variant; the cap never lowers the quantity already in the customer's own cart (e.g. customer 3, guest 2, 1 available: 3 stays). Items present in only one cart are kept as they are.</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Owner decision (2026-10-04, TASK-025); clarification confirmed the same day. API Contract §14, ADR-0031 §4. Business Spec R33.</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>R34</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Customer Account Deactivation</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>The customer deactivates from the profile after entering the current password. Final: signed out everywhere and anonymized immediately (name, email, phone, date of birth, saved addresses). Refused while the customer has an open order, an open return or a non-zero wallet balance. Orders, returns, audit and financial records keep their snapshots. Email and phone are freed for a new account; previous orders are not re-linked.</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Owner decision (2026-10-04, TASK-009). Clarifies Q154, Q46. Business Spec R34.</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>R35</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Cart Retention</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>A guest cart expires after 30 days without changes (configurable by the Owner/Admin, setting cart.guest_expiry_days); its token then starts a new empty cart. A customer cart never expires and is kept until checkout. ABANDONED is not used for expiry (left to analytics). Deactivating an account (R34) removes its active cart.</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Owner decision (2026-10-04, TASK-025). ADR-0031. Business Spec R35.</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
